--- a/review-results/复盘信息抓取-20260731.xlsx
+++ b/review-results/复盘信息抓取-20260731.xlsx
@@ -15632,15 +15632,21 @@
           <t>00:15</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
+      <c r="C2" s="3" t="n">
+        <v>36793</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>13206.17</v>
+      </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>4222</v>
       </c>
-      <c r="G2" s="3" t="n"/>
+      <c r="G2" s="3" t="n">
+        <v>5966.02</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15653,15 +15659,21 @@
           <t>00:30</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
+      <c r="C3" s="3" t="n">
+        <v>36626.9</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>12927.37</v>
+      </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>4278.5</v>
       </c>
-      <c r="G3" s="3" t="n"/>
+      <c r="G3" s="3" t="n">
+        <v>6290</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15674,15 +15686,21 @@
           <t>00:45</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
+      <c r="C4" s="3" t="n">
+        <v>36190.4</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>12341.39</v>
+      </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>4277.1</v>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="G4" s="3" t="n">
+        <v>6327.64</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15695,15 +15713,21 @@
           <t>01:00</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
+      <c r="C5" s="3" t="n">
+        <v>36002.4</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>11993.55</v>
+      </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>4167.7</v>
       </c>
-      <c r="G5" s="3" t="n"/>
+      <c r="G5" s="3" t="n">
+        <v>6274.15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15716,15 +15740,21 @@
           <t>01:15</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
+      <c r="C6" s="3" t="n">
+        <v>38137.3</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>12394.62</v>
+      </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>4140.3</v>
       </c>
-      <c r="G6" s="3" t="n"/>
+      <c r="G6" s="3" t="n">
+        <v>6943.91</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15737,15 +15767,21 @@
           <t>01:30</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
+      <c r="C7" s="3" t="n">
+        <v>38079.1</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>12393.75</v>
+      </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>4073.7</v>
       </c>
-      <c r="G7" s="3" t="n"/>
+      <c r="G7" s="3" t="n">
+        <v>6853.01</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15758,15 +15794,21 @@
           <t>01:45</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
+      <c r="C8" s="3" t="n">
+        <v>37123</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>12422.29</v>
+      </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>4022.1</v>
       </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="G8" s="3" t="n">
+        <v>6152.18</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15779,15 +15821,21 @@
           <t>02:00</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
+      <c r="C9" s="3" t="n">
+        <v>36356.2</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>12048.32</v>
+      </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>4005</v>
       </c>
-      <c r="G9" s="3" t="n"/>
+      <c r="G9" s="3" t="n">
+        <v>6430.28</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15800,15 +15848,21 @@
           <t>02:15</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
+      <c r="C10" s="3" t="n">
+        <v>35759</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>11914.26</v>
+      </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>3947.3</v>
       </c>
-      <c r="G10" s="3" t="n"/>
+      <c r="G10" s="3" t="n">
+        <v>6195.17</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15821,15 +15875,21 @@
           <t>02:30</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
+      <c r="C11" s="3" t="n">
+        <v>35204.4</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>11750.01</v>
+      </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>3919.9</v>
       </c>
-      <c r="G11" s="3" t="n"/>
+      <c r="G11" s="3" t="n">
+        <v>6067.49</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15842,15 +15902,21 @@
           <t>02:45</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
+      <c r="C12" s="3" t="n">
+        <v>34641.6</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>11589.43</v>
+      </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>3911.1</v>
       </c>
-      <c r="G12" s="3" t="n"/>
+      <c r="G12" s="3" t="n">
+        <v>6388.89</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15863,15 +15929,21 @@
           <t>03:00</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
+      <c r="C13" s="3" t="n">
+        <v>34419.4</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>11071.07</v>
+      </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>3874.8</v>
       </c>
-      <c r="G13" s="3" t="n"/>
+      <c r="G13" s="3" t="n">
+        <v>6131.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15884,15 +15956,21 @@
           <t>03:15</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
+      <c r="C14" s="3" t="n">
+        <v>34022</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>10702.1</v>
+      </c>
       <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>3692.9</v>
       </c>
-      <c r="G14" s="3" t="n"/>
+      <c r="G14" s="3" t="n">
+        <v>6223.6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15905,15 +15983,21 @@
           <t>03:30</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
+      <c r="C15" s="3" t="n">
+        <v>33691.5</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>10486.02</v>
+      </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>3628.4</v>
       </c>
-      <c r="G15" s="3" t="n"/>
+      <c r="G15" s="3" t="n">
+        <v>6169.01</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15926,15 +16010,21 @@
           <t>03:45</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
+      <c r="C16" s="3" t="n">
+        <v>33432.9</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>10270.68</v>
+      </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>3548.1</v>
       </c>
-      <c r="G16" s="3" t="n"/>
+      <c r="G16" s="3" t="n">
+        <v>6152.05</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15947,15 +16037,21 @@
           <t>04:00</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
+      <c r="C17" s="3" t="n">
+        <v>32847.3</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>10257.06</v>
+      </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>3413.8</v>
       </c>
-      <c r="G17" s="3" t="n"/>
+      <c r="G17" s="3" t="n">
+        <v>5894.12</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -15968,15 +16064,21 @@
           <t>04:15</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
+      <c r="C18" s="3" t="n">
+        <v>32872.2</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>10197.61</v>
+      </c>
       <c r="E18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>3248.8</v>
       </c>
-      <c r="G18" s="3" t="n"/>
+      <c r="G18" s="3" t="n">
+        <v>6076.5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -15989,15 +16091,21 @@
           <t>04:30</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
+      <c r="C19" s="3" t="n">
+        <v>32660.9</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>10187.89</v>
+      </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>3064.6</v>
       </c>
-      <c r="G19" s="3" t="n"/>
+      <c r="G19" s="3" t="n">
+        <v>6250.65</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -16010,15 +16118,21 @@
           <t>04:45</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
+      <c r="C20" s="3" t="n">
+        <v>32377.4</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>10027.42</v>
+      </c>
       <c r="E20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>2932.6</v>
       </c>
-      <c r="G20" s="3" t="n"/>
+      <c r="G20" s="3" t="n">
+        <v>5963.3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -16031,15 +16145,21 @@
           <t>05:00</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
+      <c r="C21" s="3" t="n">
+        <v>32435.1</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>9868.1</v>
+      </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>2910.1</v>
       </c>
-      <c r="G21" s="3" t="n"/>
+      <c r="G21" s="3" t="n">
+        <v>5911.71</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -16052,15 +16172,21 @@
           <t>05:15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
+      <c r="C22" s="3" t="n">
+        <v>32558.2</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>9859.219999999999</v>
+      </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>2846.6</v>
       </c>
-      <c r="G22" s="3" t="n"/>
+      <c r="G22" s="3" t="n">
+        <v>5967.08</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -16073,15 +16199,21 @@
           <t>05:30</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
+      <c r="C23" s="3" t="n">
+        <v>32874.9</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>9854.780000000001</v>
+      </c>
       <c r="E23" s="3" t="n">
         <v>56.1</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>2780.6</v>
       </c>
-      <c r="G23" s="3" t="n"/>
+      <c r="G23" s="3" t="n">
+        <v>6192.63</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -16094,15 +16226,21 @@
           <t>05:45</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
+      <c r="C24" s="3" t="n">
+        <v>33033.1</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>9853.76</v>
+      </c>
       <c r="E24" s="3" t="n">
         <v>198.1</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>2732.1</v>
       </c>
-      <c r="G24" s="3" t="n"/>
+      <c r="G24" s="3" t="n">
+        <v>6024.89</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -16115,15 +16253,21 @@
           <t>06:00</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
+      <c r="C25" s="3" t="n">
+        <v>33214.6</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>9853.540000000001</v>
+      </c>
       <c r="E25" s="3" t="n">
         <v>471.1</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>2714.9</v>
       </c>
-      <c r="G25" s="3" t="n"/>
+      <c r="G25" s="3" t="n">
+        <v>5891.91</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -16136,15 +16280,21 @@
           <t>06:15</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
+      <c r="C26" s="3" t="n">
+        <v>33393.7</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>9749.110000000001</v>
+      </c>
       <c r="E26" s="3" t="n">
         <v>742.7</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>2673.4</v>
       </c>
-      <c r="G26" s="3" t="n"/>
+      <c r="G26" s="3" t="n">
+        <v>5542.05</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -16157,15 +16307,21 @@
           <t>06:30</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
+      <c r="C27" s="3" t="n">
+        <v>33221</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>9759.690000000001</v>
+      </c>
       <c r="E27" s="3" t="n">
         <v>1114.6</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>2565.4</v>
       </c>
-      <c r="G27" s="3" t="n"/>
+      <c r="G27" s="3" t="n">
+        <v>5155.54</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -16178,15 +16334,21 @@
           <t>06:45</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="C28" s="3" t="n">
+        <v>33231</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>9707.67</v>
+      </c>
       <c r="E28" s="3" t="n">
         <v>1425.6</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>2441.2</v>
       </c>
-      <c r="G28" s="3" t="n"/>
+      <c r="G28" s="3" t="n">
+        <v>4910.43</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -16199,15 +16361,21 @@
           <t>07:00</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
+      <c r="C29" s="3" t="n">
+        <v>32770.9</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>9426.27</v>
+      </c>
       <c r="E29" s="3" t="n">
         <v>1602.6</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>2177.9</v>
       </c>
-      <c r="G29" s="3" t="n"/>
+      <c r="G29" s="3" t="n">
+        <v>4358.68</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -16220,15 +16388,21 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
+      <c r="C30" s="3" t="n">
+        <v>33181.7</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>9046.66</v>
+      </c>
       <c r="E30" s="3" t="n">
         <v>1890.4</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>1987.2</v>
       </c>
-      <c r="G30" s="3" t="n"/>
+      <c r="G30" s="3" t="n">
+        <v>4630.1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -16241,15 +16415,21 @@
           <t>07:30</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
+      <c r="C31" s="3" t="n">
+        <v>33395.8</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>8221.610000000001</v>
+      </c>
       <c r="E31" s="3" t="n">
         <v>2050.6</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>1792</v>
       </c>
-      <c r="G31" s="3" t="n"/>
+      <c r="G31" s="3" t="n">
+        <v>4909.53</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -16262,15 +16442,21 @@
           <t>07:45</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
+      <c r="C32" s="3" t="n">
+        <v>33995.2</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>7212.26</v>
+      </c>
       <c r="E32" s="3" t="n">
         <v>2299.1</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>1684.5</v>
       </c>
-      <c r="G32" s="3" t="n"/>
+      <c r="G32" s="3" t="n">
+        <v>5621.49</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -16283,15 +16469,21 @@
           <t>08:00</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
+      <c r="C33" s="3" t="n">
+        <v>34783.2</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>6240.01</v>
+      </c>
       <c r="E33" s="3" t="n">
         <v>2804.5</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>1623.1</v>
       </c>
-      <c r="G33" s="3" t="n"/>
+      <c r="G33" s="3" t="n">
+        <v>6719.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -16304,15 +16496,21 @@
           <t>08:15</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
+      <c r="C34" s="3" t="n">
+        <v>36303.4</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>6191.15</v>
+      </c>
       <c r="E34" s="3" t="n">
         <v>3200.7</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>1613.8</v>
       </c>
-      <c r="G34" s="3" t="n"/>
+      <c r="G34" s="3" t="n">
+        <v>6955.79</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -16325,15 +16523,21 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
+      <c r="C35" s="3" t="n">
+        <v>36893.3</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>6092.47</v>
+      </c>
       <c r="E35" s="3" t="n">
         <v>3542.4</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>1618.2</v>
       </c>
-      <c r="G35" s="3" t="n"/>
+      <c r="G35" s="3" t="n">
+        <v>7489.12</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -16346,15 +16550,21 @@
           <t>08:45</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
+      <c r="C36" s="3" t="n">
+        <v>37343.6</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>5787.65</v>
+      </c>
       <c r="E36" s="3" t="n">
         <v>3698.7</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>1575.5</v>
       </c>
-      <c r="G36" s="3" t="n"/>
+      <c r="G36" s="3" t="n">
+        <v>7833.91</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -16367,15 +16577,21 @@
           <t>09:00</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
+      <c r="C37" s="3" t="n">
+        <v>37617.3</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>5511.85</v>
+      </c>
       <c r="E37" s="3" t="n">
         <v>3761.6</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>1446.4</v>
       </c>
-      <c r="G37" s="3" t="n"/>
+      <c r="G37" s="3" t="n">
+        <v>9152.809999999999</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -16388,15 +16604,21 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
+      <c r="C38" s="3" t="n">
+        <v>38419.7</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>5540.31</v>
+      </c>
       <c r="E38" s="3" t="n">
         <v>4314.3</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>1307.4</v>
       </c>
-      <c r="G38" s="3" t="n"/>
+      <c r="G38" s="3" t="n">
+        <v>9225.33</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -16409,15 +16631,21 @@
           <t>09:30</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
+      <c r="C39" s="3" t="n">
+        <v>38389</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>5580.73</v>
+      </c>
       <c r="E39" s="3" t="n">
         <v>4804</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>1157.4</v>
       </c>
-      <c r="G39" s="3" t="n"/>
+      <c r="G39" s="3" t="n">
+        <v>8831.049999999999</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -16430,15 +16658,21 @@
           <t>09:45</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
+      <c r="C40" s="3" t="n">
+        <v>38408.3</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>5615.15</v>
+      </c>
       <c r="E40" s="3" t="n">
         <v>5314.1</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>1095.3</v>
       </c>
-      <c r="G40" s="3" t="n"/>
+      <c r="G40" s="3" t="n">
+        <v>9165.93</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -16451,15 +16685,21 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
+      <c r="C41" s="3" t="n">
+        <v>38611.1</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>5635.66</v>
+      </c>
       <c r="E41" s="3" t="n">
         <v>5934.7</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>1040.3</v>
       </c>
-      <c r="G41" s="3" t="n"/>
+      <c r="G41" s="3" t="n">
+        <v>9181.17</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -16472,15 +16712,21 @@
           <t>10:15</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n"/>
+      <c r="C42" s="3" t="n">
+        <v>38539.9</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>5661.12</v>
+      </c>
       <c r="E42" s="3" t="n">
         <v>6258</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>998.9</v>
       </c>
-      <c r="G42" s="3" t="n"/>
+      <c r="G42" s="3" t="n">
+        <v>9313.309999999999</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -16493,15 +16739,21 @@
           <t>10:30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="n"/>
+      <c r="C43" s="3" t="n">
+        <v>38439.3</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>5672.36</v>
+      </c>
       <c r="E43" s="3" t="n">
         <v>6655.8</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>916.8</v>
       </c>
-      <c r="G43" s="3" t="n"/>
+      <c r="G43" s="3" t="n">
+        <v>9165.76</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -16514,15 +16766,21 @@
           <t>10:45</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="n"/>
+      <c r="C44" s="3" t="n">
+        <v>38647.6</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>5684.46</v>
+      </c>
       <c r="E44" s="3" t="n">
         <v>6963.7</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>876.9</v>
       </c>
-      <c r="G44" s="3" t="n"/>
+      <c r="G44" s="3" t="n">
+        <v>9237.290000000001</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -16535,15 +16793,21 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
+      <c r="C45" s="3" t="n">
+        <v>38774.9</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>5694.57</v>
+      </c>
       <c r="E45" s="3" t="n">
         <v>7468.2</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>816.1</v>
       </c>
-      <c r="G45" s="3" t="n"/>
+      <c r="G45" s="3" t="n">
+        <v>9091.860000000001</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -16556,15 +16820,21 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
+      <c r="C46" s="3" t="n">
+        <v>39211.8</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>5698.51</v>
+      </c>
       <c r="E46" s="3" t="n">
         <v>7500.4</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>794</v>
       </c>
-      <c r="G46" s="3" t="n"/>
+      <c r="G46" s="3" t="n">
+        <v>9231.24</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -16577,15 +16847,21 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="C47" s="3" t="n"/>
-      <c r="D47" s="3" t="n"/>
+      <c r="C47" s="3" t="n">
+        <v>39005.7</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>5720.6</v>
+      </c>
       <c r="E47" s="3" t="n">
         <v>7813</v>
       </c>
       <c r="F47" s="3" t="n">
         <v>801.2</v>
       </c>
-      <c r="G47" s="3" t="n"/>
+      <c r="G47" s="3" t="n">
+        <v>8387.809999999999</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -16598,15 +16874,21 @@
           <t>11:45</t>
         </is>
       </c>
-      <c r="C48" s="3" t="n"/>
-      <c r="D48" s="3" t="n"/>
+      <c r="C48" s="3" t="n">
+        <v>38422.3</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>5722.46</v>
+      </c>
       <c r="E48" s="3" t="n">
         <v>8249.6</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>846.5</v>
       </c>
-      <c r="G48" s="3" t="n"/>
+      <c r="G48" s="3" t="n">
+        <v>7908.52</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -16619,15 +16901,21 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="C49" s="3" t="n"/>
-      <c r="D49" s="3" t="n"/>
+      <c r="C49" s="3" t="n">
+        <v>37952.9</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>5728.74</v>
+      </c>
       <c r="E49" s="3" t="n">
         <v>8480</v>
       </c>
       <c r="F49" s="3" t="n">
         <v>914</v>
       </c>
-      <c r="G49" s="3" t="n"/>
+      <c r="G49" s="3" t="n">
+        <v>7374.35</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -16640,15 +16928,21 @@
           <t>12:15</t>
         </is>
       </c>
-      <c r="C50" s="3" t="n"/>
-      <c r="D50" s="3" t="n"/>
+      <c r="C50" s="3" t="n">
+        <v>39617.2</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>6348.17</v>
+      </c>
       <c r="E50" s="3" t="n">
         <v>8566.299999999999</v>
       </c>
       <c r="F50" s="3" t="n">
         <v>986.5</v>
       </c>
-      <c r="G50" s="3" t="n"/>
+      <c r="G50" s="3" t="n">
+        <v>6907.48</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -16661,15 +16955,21 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
+      <c r="C51" s="3" t="n">
+        <v>40042</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>7048.51</v>
+      </c>
       <c r="E51" s="3" t="n">
         <v>8491.799999999999</v>
       </c>
       <c r="F51" s="3" t="n">
         <v>1108.6</v>
       </c>
-      <c r="G51" s="3" t="n"/>
+      <c r="G51" s="3" t="n">
+        <v>6983</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -16682,15 +16982,21 @@
           <t>12:45</t>
         </is>
       </c>
-      <c r="C52" s="3" t="n"/>
-      <c r="D52" s="3" t="n"/>
+      <c r="C52" s="3" t="n">
+        <v>39521.4</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>7771.7</v>
+      </c>
       <c r="E52" s="3" t="n">
         <v>8313.799999999999</v>
       </c>
       <c r="F52" s="3" t="n">
         <v>1145.6</v>
       </c>
-      <c r="G52" s="3" t="n"/>
+      <c r="G52" s="3" t="n">
+        <v>6647.74</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -16703,15 +17009,21 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="C53" s="3" t="n"/>
-      <c r="D53" s="3" t="n"/>
+      <c r="C53" s="3" t="n">
+        <v>39442</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>8476.73</v>
+      </c>
       <c r="E53" s="3" t="n">
         <v>7639</v>
       </c>
       <c r="F53" s="3" t="n">
         <v>1277.6</v>
       </c>
-      <c r="G53" s="3" t="n"/>
+      <c r="G53" s="3" t="n">
+        <v>7027.79</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -16724,15 +17036,21 @@
           <t>13:15</t>
         </is>
       </c>
-      <c r="C54" s="3" t="n"/>
-      <c r="D54" s="3" t="n"/>
+      <c r="C54" s="3" t="n">
+        <v>39390.3</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>9170.77</v>
+      </c>
       <c r="E54" s="3" t="n">
         <v>7244.3</v>
       </c>
       <c r="F54" s="3" t="n">
         <v>1373.6</v>
       </c>
-      <c r="G54" s="3" t="n"/>
+      <c r="G54" s="3" t="n">
+        <v>6900.79</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -16745,15 +17063,21 @@
           <t>13:30</t>
         </is>
       </c>
-      <c r="C55" s="3" t="n"/>
-      <c r="D55" s="3" t="n"/>
+      <c r="C55" s="3" t="n">
+        <v>39052.1</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>9868.27</v>
+      </c>
       <c r="E55" s="3" t="n">
         <v>7006.6</v>
       </c>
       <c r="F55" s="3" t="n">
         <v>1517.6</v>
       </c>
-      <c r="G55" s="3" t="n"/>
+      <c r="G55" s="3" t="n">
+        <v>7337.19</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -16766,15 +17090,21 @@
           <t>13:45</t>
         </is>
       </c>
-      <c r="C56" s="3" t="n"/>
-      <c r="D56" s="3" t="n"/>
+      <c r="C56" s="3" t="n">
+        <v>39247.7</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>10733.13</v>
+      </c>
       <c r="E56" s="3" t="n">
         <v>6659.1</v>
       </c>
       <c r="F56" s="3" t="n">
         <v>1693.1</v>
       </c>
-      <c r="G56" s="3" t="n"/>
+      <c r="G56" s="3" t="n">
+        <v>7239.22</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -16787,15 +17117,21 @@
           <t>14:00</t>
         </is>
       </c>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="n"/>
+      <c r="C57" s="3" t="n">
+        <v>38527.2</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>11079.45</v>
+      </c>
       <c r="E57" s="3" t="n">
         <v>6047.7</v>
       </c>
       <c r="F57" s="3" t="n">
         <v>1911.6</v>
       </c>
-      <c r="G57" s="3" t="n"/>
+      <c r="G57" s="3" t="n">
+        <v>7908.82</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -16808,15 +17144,21 @@
           <t>14:15</t>
         </is>
       </c>
-      <c r="C58" s="3" t="n"/>
-      <c r="D58" s="3" t="n"/>
+      <c r="C58" s="3" t="n">
+        <v>38263</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>11316.1</v>
+      </c>
       <c r="E58" s="3" t="n">
         <v>5453.3</v>
       </c>
       <c r="F58" s="3" t="n">
         <v>2111.9</v>
       </c>
-      <c r="G58" s="3" t="n"/>
+      <c r="G58" s="3" t="n">
+        <v>8151.77</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -16829,15 +17171,21 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="C59" s="3" t="n"/>
-      <c r="D59" s="3" t="n"/>
+      <c r="C59" s="3" t="n">
+        <v>38959.4</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>11558.72</v>
+      </c>
       <c r="E59" s="3" t="n">
         <v>5100.5</v>
       </c>
       <c r="F59" s="3" t="n">
         <v>2278.4</v>
       </c>
-      <c r="G59" s="3" t="n"/>
+      <c r="G59" s="3" t="n">
+        <v>8850.450000000001</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -16850,15 +17198,21 @@
           <t>14:45</t>
         </is>
       </c>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
+      <c r="C60" s="3" t="n">
+        <v>39190.7</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>11554.01</v>
+      </c>
       <c r="E60" s="3" t="n">
         <v>4858.8</v>
       </c>
       <c r="F60" s="3" t="n">
         <v>2452.3</v>
       </c>
-      <c r="G60" s="3" t="n"/>
+      <c r="G60" s="3" t="n">
+        <v>8586.32</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -16871,15 +17225,21 @@
           <t>15:00</t>
         </is>
       </c>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="n"/>
+      <c r="C61" s="3" t="n">
+        <v>39456.3</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>11735.08</v>
+      </c>
       <c r="E61" s="3" t="n">
         <v>4583</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>2616.3</v>
       </c>
-      <c r="G61" s="3" t="n"/>
+      <c r="G61" s="3" t="n">
+        <v>8308.32</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -16892,15 +17252,21 @@
           <t>15:15</t>
         </is>
       </c>
-      <c r="C62" s="3" t="n"/>
-      <c r="D62" s="3" t="n"/>
+      <c r="C62" s="3" t="n">
+        <v>39867.1</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>12284.95</v>
+      </c>
       <c r="E62" s="3" t="n">
         <v>3937.2</v>
       </c>
       <c r="F62" s="3" t="n">
         <v>2835.4</v>
       </c>
-      <c r="G62" s="3" t="n"/>
+      <c r="G62" s="3" t="n">
+        <v>8264.799999999999</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -16913,15 +17279,21 @@
           <t>15:30</t>
         </is>
       </c>
-      <c r="C63" s="3" t="n"/>
-      <c r="D63" s="3" t="n"/>
+      <c r="C63" s="3" t="n">
+        <v>40469.4</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>12768.8</v>
+      </c>
       <c r="E63" s="3" t="n">
         <v>3581.8</v>
       </c>
       <c r="F63" s="3" t="n">
         <v>2855.4</v>
       </c>
-      <c r="G63" s="3" t="n"/>
+      <c r="G63" s="3" t="n">
+        <v>8649.280000000001</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -16934,15 +17306,21 @@
           <t>15:45</t>
         </is>
       </c>
-      <c r="C64" s="3" t="n"/>
-      <c r="D64" s="3" t="n"/>
+      <c r="C64" s="3" t="n">
+        <v>40813.6</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>12945.4</v>
+      </c>
       <c r="E64" s="3" t="n">
         <v>3404.7</v>
       </c>
       <c r="F64" s="3" t="n">
         <v>3002</v>
       </c>
-      <c r="G64" s="3" t="n"/>
+      <c r="G64" s="3" t="n">
+        <v>8439.18</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -16955,15 +17333,21 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="C65" s="3" t="n"/>
-      <c r="D65" s="3" t="n"/>
+      <c r="C65" s="3" t="n">
+        <v>41211</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>13019.33</v>
+      </c>
       <c r="E65" s="3" t="n">
         <v>3189.4</v>
       </c>
       <c r="F65" s="3" t="n">
         <v>3133.5</v>
       </c>
-      <c r="G65" s="3" t="n"/>
+      <c r="G65" s="3" t="n">
+        <v>8556.459999999999</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -16976,15 +17360,21 @@
           <t>16:15</t>
         </is>
       </c>
-      <c r="C66" s="3" t="n"/>
-      <c r="D66" s="3" t="n"/>
+      <c r="C66" s="3" t="n">
+        <v>41862.4</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>12980.24</v>
+      </c>
       <c r="E66" s="3" t="n">
         <v>3054.8</v>
       </c>
       <c r="F66" s="3" t="n">
         <v>3233.2</v>
       </c>
-      <c r="G66" s="3" t="n"/>
+      <c r="G66" s="3" t="n">
+        <v>8368.940000000001</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -16997,15 +17387,21 @@
           <t>16:30</t>
         </is>
       </c>
-      <c r="C67" s="3" t="n"/>
-      <c r="D67" s="3" t="n"/>
+      <c r="C67" s="3" t="n">
+        <v>42615.9</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>13086.36</v>
+      </c>
       <c r="E67" s="3" t="n">
         <v>2843.9</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>3224.8</v>
       </c>
-      <c r="G67" s="3" t="n"/>
+      <c r="G67" s="3" t="n">
+        <v>8401.959999999999</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -17018,15 +17414,21 @@
           <t>16:45</t>
         </is>
       </c>
-      <c r="C68" s="3" t="n"/>
-      <c r="D68" s="3" t="n"/>
+      <c r="C68" s="3" t="n">
+        <v>43000.8</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>13196.67</v>
+      </c>
       <c r="E68" s="3" t="n">
         <v>2491.5</v>
       </c>
       <c r="F68" s="3" t="n">
         <v>3231.2</v>
       </c>
-      <c r="G68" s="3" t="n"/>
+      <c r="G68" s="3" t="n">
+        <v>8330.35</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -17039,15 +17441,21 @@
           <t>17:00</t>
         </is>
       </c>
-      <c r="C69" s="3" t="n"/>
-      <c r="D69" s="3" t="n"/>
+      <c r="C69" s="3" t="n">
+        <v>43605.9</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>13253.6</v>
+      </c>
       <c r="E69" s="3" t="n">
         <v>1895.3</v>
       </c>
       <c r="F69" s="3" t="n">
         <v>3353.3</v>
       </c>
-      <c r="G69" s="3" t="n"/>
+      <c r="G69" s="3" t="n">
+        <v>8327.280000000001</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -17060,15 +17468,21 @@
           <t>17:15</t>
         </is>
       </c>
-      <c r="C70" s="3" t="n"/>
-      <c r="D70" s="3" t="n"/>
+      <c r="C70" s="3" t="n">
+        <v>43844.1</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>13208.35</v>
+      </c>
       <c r="E70" s="3" t="n">
         <v>1549.5</v>
       </c>
       <c r="F70" s="3" t="n">
         <v>3689.1</v>
       </c>
-      <c r="G70" s="3" t="n"/>
+      <c r="G70" s="3" t="n">
+        <v>8646.309999999999</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -17081,15 +17495,21 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="C71" s="3" t="n"/>
-      <c r="D71" s="3" t="n"/>
+      <c r="C71" s="3" t="n">
+        <v>43737.7</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>13170.91</v>
+      </c>
       <c r="E71" s="3" t="n">
         <v>1162.6</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>4083.5</v>
       </c>
-      <c r="G71" s="3" t="n"/>
+      <c r="G71" s="3" t="n">
+        <v>9176.74</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -17102,15 +17522,21 @@
           <t>17:45</t>
         </is>
       </c>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="3" t="n"/>
+      <c r="C72" s="3" t="n">
+        <v>43703.6</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>13279.56</v>
+      </c>
       <c r="E72" s="3" t="n">
         <v>891.7</v>
       </c>
       <c r="F72" s="3" t="n">
         <v>4511.6</v>
       </c>
-      <c r="G72" s="3" t="n"/>
+      <c r="G72" s="3" t="n">
+        <v>10054.34</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -17123,15 +17549,21 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="n"/>
+      <c r="C73" s="3" t="n">
+        <v>43670.5</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>13554.25</v>
+      </c>
       <c r="E73" s="3" t="n">
         <v>601.6</v>
       </c>
       <c r="F73" s="3" t="n">
         <v>4814.4</v>
       </c>
-      <c r="G73" s="3" t="n"/>
+      <c r="G73" s="3" t="n">
+        <v>10756.3</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -17144,15 +17576,21 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
+      <c r="C74" s="3" t="n">
+        <v>43208.8</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>13780.53</v>
+      </c>
       <c r="E74" s="3" t="n">
         <v>473.3</v>
       </c>
       <c r="F74" s="3" t="n">
         <v>4619.1</v>
       </c>
-      <c r="G74" s="3" t="n"/>
+      <c r="G74" s="3" t="n">
+        <v>11284.59</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -17165,15 +17603,21 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="C75" s="3" t="n"/>
-      <c r="D75" s="3" t="n"/>
+      <c r="C75" s="3" t="n">
+        <v>43153.7</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>14008.63</v>
+      </c>
       <c r="E75" s="3" t="n">
         <v>354.7</v>
       </c>
       <c r="F75" s="3" t="n">
         <v>4418.7</v>
       </c>
-      <c r="G75" s="3" t="n"/>
+      <c r="G75" s="3" t="n">
+        <v>11228.44</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -17186,15 +17630,21 @@
           <t>18:45</t>
         </is>
       </c>
-      <c r="C76" s="3" t="n"/>
-      <c r="D76" s="3" t="n"/>
+      <c r="C76" s="3" t="n">
+        <v>43027.6</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>14093.96</v>
+      </c>
       <c r="E76" s="3" t="n">
         <v>232.7</v>
       </c>
       <c r="F76" s="3" t="n">
         <v>4352.5</v>
       </c>
-      <c r="G76" s="3" t="n"/>
+      <c r="G76" s="3" t="n">
+        <v>11336.77</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -17207,15 +17657,21 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="C77" s="3" t="n"/>
-      <c r="D77" s="3" t="n"/>
+      <c r="C77" s="3" t="n">
+        <v>42839.3</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>14086.49</v>
+      </c>
       <c r="E77" s="3" t="n">
         <v>114</v>
       </c>
       <c r="F77" s="3" t="n">
         <v>4495</v>
       </c>
-      <c r="G77" s="3" t="n"/>
+      <c r="G77" s="3" t="n">
+        <v>11283.36</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -17228,15 +17684,21 @@
           <t>19:15</t>
         </is>
       </c>
-      <c r="C78" s="3" t="n"/>
-      <c r="D78" s="3" t="n"/>
+      <c r="C78" s="3" t="n">
+        <v>42581.6</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>14090.03</v>
+      </c>
       <c r="E78" s="3" t="n">
         <v>41.4</v>
       </c>
       <c r="F78" s="3" t="n">
         <v>4492.9</v>
       </c>
-      <c r="G78" s="3" t="n"/>
+      <c r="G78" s="3" t="n">
+        <v>11514.27</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -17249,15 +17711,21 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="C79" s="3" t="n"/>
-      <c r="D79" s="3" t="n"/>
+      <c r="C79" s="3" t="n">
+        <v>43080.6</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>14099.59</v>
+      </c>
       <c r="E79" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F79" s="3" t="n">
         <v>4198.5</v>
       </c>
-      <c r="G79" s="3" t="n"/>
+      <c r="G79" s="3" t="n">
+        <v>11904.52</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -17270,15 +17738,21 @@
           <t>19:45</t>
         </is>
       </c>
-      <c r="C80" s="3" t="n"/>
-      <c r="D80" s="3" t="n"/>
+      <c r="C80" s="3" t="n">
+        <v>42908.5</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>14110.86</v>
+      </c>
       <c r="E80" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F80" s="3" t="n">
         <v>4484.9</v>
       </c>
-      <c r="G80" s="3" t="n"/>
+      <c r="G80" s="3" t="n">
+        <v>11704</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -17291,15 +17765,21 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="C81" s="3" t="n"/>
-      <c r="D81" s="3" t="n"/>
+      <c r="C81" s="3" t="n">
+        <v>42588</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>14124.33</v>
+      </c>
       <c r="E81" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F81" s="3" t="n">
         <v>4366.5</v>
       </c>
-      <c r="G81" s="3" t="n"/>
+      <c r="G81" s="3" t="n">
+        <v>11613.39</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -17312,15 +17792,21 @@
           <t>20:15</t>
         </is>
       </c>
-      <c r="C82" s="3" t="n"/>
-      <c r="D82" s="3" t="n"/>
+      <c r="C82" s="3" t="n">
+        <v>42593.8</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>14127.3</v>
+      </c>
       <c r="E82" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="3" t="n">
         <v>4039.4</v>
       </c>
-      <c r="G82" s="3" t="n"/>
+      <c r="G82" s="3" t="n">
+        <v>11726.49</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -17333,15 +17819,21 @@
           <t>20:30</t>
         </is>
       </c>
-      <c r="C83" s="3" t="n"/>
-      <c r="D83" s="3" t="n"/>
+      <c r="C83" s="3" t="n">
+        <v>42326.2</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>14084.03</v>
+      </c>
       <c r="E83" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F83" s="3" t="n">
         <v>3763.7</v>
       </c>
-      <c r="G83" s="3" t="n"/>
+      <c r="G83" s="3" t="n">
+        <v>11561.38</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -17354,15 +17846,21 @@
           <t>20:45</t>
         </is>
       </c>
-      <c r="C84" s="3" t="n"/>
-      <c r="D84" s="3" t="n"/>
+      <c r="C84" s="3" t="n">
+        <v>41997.3</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>14038.62</v>
+      </c>
       <c r="E84" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F84" s="3" t="n">
         <v>3713.4</v>
       </c>
-      <c r="G84" s="3" t="n"/>
+      <c r="G84" s="3" t="n">
+        <v>11544.92</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -17375,15 +17873,21 @@
           <t>21:00</t>
         </is>
       </c>
-      <c r="C85" s="3" t="n"/>
-      <c r="D85" s="3" t="n"/>
+      <c r="C85" s="3" t="n">
+        <v>41522.9</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>13988.63</v>
+      </c>
       <c r="E85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F85" s="3" t="n">
         <v>3857.4</v>
       </c>
-      <c r="G85" s="3" t="n"/>
+      <c r="G85" s="3" t="n">
+        <v>11501.36</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -17396,15 +17900,21 @@
           <t>21:15</t>
         </is>
       </c>
-      <c r="C86" s="3" t="n"/>
-      <c r="D86" s="3" t="n"/>
+      <c r="C86" s="3" t="n">
+        <v>41114</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>13951.51</v>
+      </c>
       <c r="E86" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F86" s="3" t="n">
         <v>3753.8</v>
       </c>
-      <c r="G86" s="3" t="n"/>
+      <c r="G86" s="3" t="n">
+        <v>11276.5</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -17417,15 +17927,21 @@
           <t>21:30</t>
         </is>
       </c>
-      <c r="C87" s="3" t="n"/>
-      <c r="D87" s="3" t="n"/>
+      <c r="C87" s="3" t="n">
+        <v>41056.4</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>13954.41</v>
+      </c>
       <c r="E87" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F87" s="3" t="n">
         <v>3763.1</v>
       </c>
-      <c r="G87" s="3" t="n"/>
+      <c r="G87" s="3" t="n">
+        <v>10741.23</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -17438,15 +17954,21 @@
           <t>21:45</t>
         </is>
       </c>
-      <c r="C88" s="3" t="n"/>
-      <c r="D88" s="3" t="n"/>
+      <c r="C88" s="3" t="n">
+        <v>40351</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>13858.06</v>
+      </c>
       <c r="E88" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F88" s="3" t="n">
         <v>3915.7</v>
       </c>
-      <c r="G88" s="3" t="n"/>
+      <c r="G88" s="3" t="n">
+        <v>10118.53</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -17459,15 +17981,21 @@
           <t>22:00</t>
         </is>
       </c>
-      <c r="C89" s="3" t="n"/>
-      <c r="D89" s="3" t="n"/>
+      <c r="C89" s="3" t="n">
+        <v>39982.3</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>13609.17</v>
+      </c>
       <c r="E89" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F89" s="3" t="n">
         <v>3871.5</v>
       </c>
-      <c r="G89" s="3" t="n"/>
+      <c r="G89" s="3" t="n">
+        <v>9838.66</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -17480,15 +18008,21 @@
           <t>22:15</t>
         </is>
       </c>
-      <c r="C90" s="3" t="n"/>
-      <c r="D90" s="3" t="n"/>
+      <c r="C90" s="3" t="n">
+        <v>39379.3</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>12639.15</v>
+      </c>
       <c r="E90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F90" s="3" t="n">
         <v>3602.4</v>
       </c>
-      <c r="G90" s="3" t="n"/>
+      <c r="G90" s="3" t="n">
+        <v>9013.66</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -17501,15 +18035,21 @@
           <t>22:30</t>
         </is>
       </c>
-      <c r="C91" s="3" t="n"/>
-      <c r="D91" s="3" t="n"/>
+      <c r="C91" s="3" t="n">
+        <v>38945.6</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>12245.62</v>
+      </c>
       <c r="E91" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F91" s="3" t="n">
         <v>3371.6</v>
       </c>
-      <c r="G91" s="3" t="n"/>
+      <c r="G91" s="3" t="n">
+        <v>8329.48</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -17522,15 +18062,21 @@
           <t>22:45</t>
         </is>
       </c>
-      <c r="C92" s="3" t="n"/>
-      <c r="D92" s="3" t="n"/>
+      <c r="C92" s="3" t="n">
+        <v>37979.9</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>11953.43</v>
+      </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>3112.6</v>
       </c>
-      <c r="G92" s="3" t="n"/>
+      <c r="G92" s="3" t="n">
+        <v>7364.94</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -17543,15 +18089,21 @@
           <t>23:00</t>
         </is>
       </c>
-      <c r="C93" s="3" t="n"/>
-      <c r="D93" s="3" t="n"/>
+      <c r="C93" s="3" t="n">
+        <v>37319.6</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>11765.31</v>
+      </c>
       <c r="E93" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F93" s="3" t="n">
         <v>2951.2</v>
       </c>
-      <c r="G93" s="3" t="n"/>
+      <c r="G93" s="3" t="n">
+        <v>6831.04</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -17564,15 +18116,21 @@
           <t>23:15</t>
         </is>
       </c>
-      <c r="C94" s="3" t="n"/>
-      <c r="D94" s="3" t="n"/>
+      <c r="C94" s="3" t="n">
+        <v>36477.1</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>11569.57</v>
+      </c>
       <c r="E94" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F94" s="3" t="n">
         <v>2976</v>
       </c>
-      <c r="G94" s="3" t="n"/>
+      <c r="G94" s="3" t="n">
+        <v>6223.79</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -17585,15 +18143,21 @@
           <t>23:30</t>
         </is>
       </c>
-      <c r="C95" s="3" t="n"/>
-      <c r="D95" s="3" t="n"/>
+      <c r="C95" s="3" t="n">
+        <v>35971.8</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>11371.62</v>
+      </c>
       <c r="E95" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F95" s="3" t="n">
         <v>2942</v>
       </c>
-      <c r="G95" s="3" t="n"/>
+      <c r="G95" s="3" t="n">
+        <v>6222.08</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -17606,15 +18170,21 @@
           <t>23:45</t>
         </is>
       </c>
-      <c r="C96" s="3" t="n"/>
-      <c r="D96" s="3" t="n"/>
+      <c r="C96" s="3" t="n">
+        <v>35377.4</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>11174.36</v>
+      </c>
       <c r="E96" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F96" s="3" t="n">
         <v>2910.3</v>
       </c>
-      <c r="G96" s="3" t="n"/>
+      <c r="G96" s="3" t="n">
+        <v>6097.34</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -17627,15 +18197,21 @@
           <t>24:00</t>
         </is>
       </c>
-      <c r="C97" s="3" t="n"/>
-      <c r="D97" s="3" t="n"/>
+      <c r="C97" s="3" t="n">
+        <v>34971</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>11001.5</v>
+      </c>
       <c r="E97" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F97" s="3" t="n">
         <v>2872.9</v>
       </c>
-      <c r="G97" s="3" t="n"/>
+      <c r="G97" s="3" t="n">
+        <v>5928.24</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17648,7 +18224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -17754,24 +18330,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>新能源实际发电曲线</t>
+          <t>各时段各类电源电量</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>960</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>各时段各类电源电量</t>
+          <t>各时段各类电源的开机台数</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>960</v>
+        <v>768</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
@@ -17780,91 +18356,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>各时段各类电源的开机台数</t>
+          <t>实时储能充电计划及电价</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>768</v>
+        <v>96</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>日前非市场化机组总出力</t>
+          <t>日前储能充电计划及电价</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>96</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>新能源实际发电曲线</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>96</v>
-      </c>
-      <c r="C12" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>实际系统负荷</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>96</v>
-      </c>
-      <c r="C13" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>省间联络线输电情况</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>96</v>
-      </c>
-      <c r="C14" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>实时储能充电计划及电价</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>96</v>
-      </c>
-      <c r="C15" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>日前储能充电计划及电价</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>96</v>
-      </c>
-      <c r="C16" t="n">
         <v>9</v>
       </c>
     </row>

--- a/review-results/复盘信息抓取-20260731.xlsx
+++ b/review-results/复盘信息抓取-20260731.xlsx
@@ -1043,20 +1043,20 @@
   <dimension ref="A1:T97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="17" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
@@ -5049,17 +5049,15 @@
   <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="2"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="7"/>
-    <col width="22" customWidth="1" min="8" max="9"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="8" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6184,33 +6182,31 @@
   <dimension ref="A1:AB97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="24"/>
-    <col width="8" customWidth="1" min="24" max="24"/>
-    <col width="8" customWidth="1" min="25" max="26"/>
-    <col width="8" customWidth="1" min="26" max="26"/>
-    <col width="8" customWidth="1" min="27" max="27"/>
-    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="24"/>
+    <col width="5" customWidth="1" min="25" max="26"/>
+    <col width="6" customWidth="1" min="27" max="27"/>
+    <col width="7" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15576,12 +15572,11 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="6"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18227,9 +18222,9 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
